--- a/output/resumen.xlsx
+++ b/output/resumen.xlsx
@@ -4507,7 +4507,7 @@
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
-          <t>LUNES</t>
+          <t>MARTES</t>
         </is>
       </c>
       <c r="J50" t="inlineStr"/>
@@ -4519,7 +4519,7 @@
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-23, 2026-02-24</t>
+          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -4545,7 +4545,7 @@
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-10, 2026-02-23</t>
+          <t>2026-02-03, 2026-02-10</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
@@ -4554,13 +4554,13 @@
         </is>
       </c>
       <c r="U50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V50" t="n">
         <v>2</v>
       </c>
       <c r="W50" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="X50" t="n">
         <v>0.5</v>

--- a/output/resumen.xlsx
+++ b/output/resumen.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X3"/>
+  <dimension ref="A1:X47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -541,181 +541,3687 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BOGOTA</t>
+          <t xml:space="preserve">BOGOTA </t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BURDEOS CIUDAD LA SALLE</t>
+          <t>ABADIA SAN RAFAEL</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Ejecución</t>
+          <t>Entregas</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Pedro Mora</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Fabian Gutierrez</t>
-        </is>
-      </c>
+          <t>Ronald Forero</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>LUNES</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>MARTES</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-24, 2026-03-25</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-09, 2026-03-16, 2026-03-24, 2026-03-30</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-11, 2026-03-18, 2026-03-25</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>2026-03-02, 2026-03-09, 2026-03-16, 2026-03-24</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>2026-03-04, 2026-03-11, 2026-03-18, 2026-03-25</t>
-        </is>
-      </c>
+          <t>2026-03-03, 2026-03-04</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
       <c r="U2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BOGOTA</t>
+          <t xml:space="preserve">BOGOTA </t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CHAMONIX CIUDAD LA SALLE</t>
+          <t>ARAGON</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ejecución</t>
+          <t>Entregas</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Pedro Mora</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Licette Koop</t>
-        </is>
-      </c>
+          <t>Ronald Forero</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr">
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BOGOTA </t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>BAVIERA</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Entregas</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Pedro Mora</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BOGOTA </t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>BURDEOS CIUDAD LA SALLE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Pedro Mora</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Fabian Enrique Gutierrez Tole</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>CIUDAD LA SALLE</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>LUNES</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>MIERCOLES</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-24, 2026-03-25</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>4</v>
+      </c>
+      <c r="P5" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>2026-03-02, 2026-03-09</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>2026-03-04, 2026-03-11</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>2026-03-02, 2026-03-09</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>2026-03-04, 2026-03-11</t>
+        </is>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
+      </c>
+      <c r="V5" t="n">
+        <v>2</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BOGOTA </t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>BURGOS CASTILLA RESERVADO</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Entregas</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Ronald Forero</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>2026-03-02, 2026-03-03</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>2026-03-02, 2026-03-03</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BOGOTA </t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>CADIZ</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Entregas</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Ronald Forero</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BOGOTA </t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>CHAMONIX CIUDAD LA SALLE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Pedro Mora</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Licette Tatiana Koop Santa</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>CIUDAD LA SALLE</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>LUNES</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>MIERCOLES</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-24, 2026-03-25</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
+        <v>4</v>
+      </c>
+      <c r="P8" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>2026-03-02, 2026-03-09</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>2026-03-02, 2026-03-09</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BOGOTA </t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>EL CAMPO</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Ronald Forero</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Juan Sebastian Ardila Castañeda</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>TRES QUEBRADAS</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
         <is>
           <t>MARTES</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>JUEVES</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
+        <v>4</v>
+      </c>
+      <c r="P9" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>2026-03-03, 2026-03-10</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>2026-03-03, 2026-03-10</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="n">
+        <v>2</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BOGOTA </t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>EL CASTELL IBERIA RESERVADO</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Ronald Forero</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Doriam Mayreth Sanchez Saenz</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>IBERIA</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>JUEVES</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>LUNES</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-24, 2026-03-25</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
+        <v>4</v>
+      </c>
+      <c r="P10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>2026-03-02, 2026-03-04, 2026-03-05</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>2026-03-02, 2026-03-04, 2026-03-09</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>2026-03-02, 2026-03-09</t>
+        </is>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V10" t="n">
+        <v>2</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BOGOTA </t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>GALLET CIUDAD LA SALLE</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Entregas</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Pedro Mora</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>2026-03-06, 2026-03-09</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BOGOTA </t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>IZOLA ZENTRAL-CITIZZEN</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Pedro Mora</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Maicol David Sanchez Ortiz</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>ZENTRAL</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
         <is>
           <t>MIERCOLES</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>JUEVES</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+        </is>
+      </c>
+      <c r="O12" t="n">
+        <v>4</v>
+      </c>
+      <c r="P12" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BOGOTA </t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>LA ALMERIA ALSACIA RESERVADO</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Pedro Mora</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Nidia Esperanza Herrera Padilla</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>ALSACIA RESERVADO</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>JUEVES</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>VIERNES</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
+        </is>
+      </c>
+      <c r="O13" t="n">
+        <v>4</v>
+      </c>
+      <c r="P13" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BOGOTA </t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>LA CABRERA</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Ronald Forero</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Martin Rafael Bohorquez Marrugo</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>TRES QUEBRADAS</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>JUEVES</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>VIERNES</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
+        </is>
+      </c>
+      <c r="O14" t="n">
+        <v>4</v>
+      </c>
+      <c r="P14" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>2026-03-03, 2026-03-05</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>2026-03-03, 2026-03-06</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BOGOTA </t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>LA CRUZ</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Entregas</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Ronald Forero</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BOGOTA </t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>LA PALMA</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Entregas</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Ronald Forero</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>2026-03-02, 2026-03-03, 2026-03-04</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>2026-03-02, 2026-03-03, 2026-03-04</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BOGOTA </t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>LA PEÑA</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Ronald Forero</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Jose Alejandro Barcenas Moreno</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>TRES QUEBRADAS</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>MIERCOLES</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>VIERNES</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
+        </is>
+      </c>
+      <c r="O17" t="n">
+        <v>4</v>
+      </c>
+      <c r="P17" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>2026-03-04, 2026-03-09</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BOGOTA </t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>LA SCALA</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Ronald Forero</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Javier Manuel Gonzalez Angulo</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>LA SCALA</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>MIERCOLES</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>MIERCOLES</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+        </is>
+      </c>
+      <c r="O18" t="n">
+        <v>4</v>
+      </c>
+      <c r="P18" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BOGOTA </t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>LA TERRA ALSACIA RESERVADO</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Pedro Mora</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Nidia Esperanza Herrera Padilla</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>ALSACIA RESERVADO</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>JUEVES</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>VIERNES</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
+        </is>
+      </c>
+      <c r="O19" t="n">
+        <v>4</v>
+      </c>
+      <c r="P19" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BOGOTA </t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>LINZ E1</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Entregas</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Pedro Mora</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BOGOTA </t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>LOIRA CIUDAD LA SALLE</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Entregas</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Pedro Mora</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BOGOTA </t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>LORCA</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Ronald Forero</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Johanna Diaz Mora</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>IBERIA</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>MIERCOLES</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>JUEVES</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+        </is>
+      </c>
+      <c r="O22" t="n">
+        <v>4</v>
+      </c>
+      <c r="P22" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="n">
+        <v>1</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BOGOTA </t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>LYON 2 CIUDAD LA SALLE</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Entregas</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Pedro Mora</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BOGOTA </t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>LYON CIUDAD LA SALLE</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Entregas</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Pedro Mora</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BOGOTA </t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>METROPOLI 30</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Pedro Mora</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Yorleynis Montejo Ruiz</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>METROPOLI 30</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>MARTES</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>JUEVES</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
         <is>
           <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+        </is>
+      </c>
+      <c r="O25" t="n">
+        <v>4</v>
+      </c>
+      <c r="P25" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>2026-03-03, 2026-03-10</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>2026-03-03, 2026-03-10</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="U25" t="n">
+        <v>2</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BOGOTA </t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>MONTPELLIER CIUDAD LA SALLE</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Pedro Mora</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Juan Alberto Gutierrez Forero</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>CIUDAD LA SALLE</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>JUEVES</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>VIERNES</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
+        </is>
+      </c>
+      <c r="O26" t="n">
+        <v>4</v>
+      </c>
+      <c r="P26" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>2026-03-04, 2026-03-06</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BOGOTA </t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>PASEO DE SEVILLA</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Entregas</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Ronald Forero</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>2026-03-03, 2026-03-10</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>2026-03-03, 2026-03-10</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BOGOTA </t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>PASEO SAN RAFAEL</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Ronald Forero</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Yuli Maribel Arias Cifuentes</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>ZIPAQUIRA</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>MARTES</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>VIERNES</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
+        </is>
+      </c>
+      <c r="O28" t="n">
+        <v>4</v>
+      </c>
+      <c r="P28" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BOGOTA </t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>PEÑAZUL EL POBLADO</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Entregas</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Ronald Forero</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BOGOTA </t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>PEÑON DE ALICANTE</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Ronald Forero</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Jennifer Paola Lopez Vaca</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>IBERIA</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>LUNES</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>09:30:00</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>MARTES</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-24, 2026-03-25</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25</t>
+        </is>
+      </c>
+      <c r="O30" t="n">
+        <v>4</v>
+      </c>
+      <c r="P30" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>2026-03-02, 2026-03-09</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>2026-03-02, 2026-03-09</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>2026-03-02, 2026-03-09</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="n">
+        <v>2</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BOGOTA </t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>PROVENZA PRESTIGE</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Entregas</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Pedro Mora</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BOGOTA </t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>SAINT MICHEL CIUDAD LA SALLE</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Pedro Mora</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Jhon Alexander Guarin Reina</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>CIUDAD LA SALLE</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>MARTES</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>JUEVES</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+        </is>
+      </c>
+      <c r="O32" t="n">
+        <v>4</v>
+      </c>
+      <c r="P32" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BOGOTA </t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>SAN LUCAS LA QUINTA</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Entregas</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Ronald Forero</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>2026-03-02, 2026-03-03</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>2026-03-02, 2026-03-03</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BOGOTA </t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>SAN MATEO - LA QUINTA</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Ronald Forero</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Zuri Andreina Orduz Sepulveda</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>ZIPAQUIRA</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>MARTES</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>09:30:00</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>MIERCOLES</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>09:30:00</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
         <is>
           <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
         </is>
       </c>
-      <c r="O3" t="n">
-        <v>4</v>
-      </c>
-      <c r="P3" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>2026-03-02, 2026-03-09, 2026-03-16, 2026-03-25</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>2026-03-05, 2026-03-11, 2026-03-18, 2026-03-26</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>2026-03-05, 2026-03-11, 2026-03-18, 2026-03-26</t>
-        </is>
-      </c>
-      <c r="U3" t="n">
+      <c r="O34" t="n">
+        <v>4</v>
+      </c>
+      <c r="P34" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>2026-03-03, 2026-03-05</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>2026-03-04, 2026-03-05</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="U34" t="n">
         <v>1</v>
       </c>
-      <c r="V3" t="n">
-        <v>4</v>
-      </c>
-      <c r="W3" t="n">
+      <c r="V34" t="n">
+        <v>1</v>
+      </c>
+      <c r="W34" t="n">
         <v>0.25</v>
       </c>
-      <c r="X3" t="n">
+      <c r="X34" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BOGOTA </t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>SAN SEBASTIAN LA QUINTA</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Ronald Forero</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Yuli Maribel Arias Cifuentes</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>ZIPAQUIRA</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>MIERCOLES</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>VIERNES</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
+        </is>
+      </c>
+      <c r="O35" t="n">
+        <v>4</v>
+      </c>
+      <c r="P35" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="n">
         <v>1</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="X35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BOGOTA </t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>SAN SIMON LA QUINTA</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Entregas</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Ronald Forero</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>2026-03-04, 2026-03-05</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>2026-03-04, 2026-03-05</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0</v>
+      </c>
+      <c r="X36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BOGOTA </t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>URB EXTERNO CIUDAD LA SALLE</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Pedro Mora</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Dario Acosta Rubiano</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>CIUDAD LA SALLE</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>MIERCOLES</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>JUEVES</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+        </is>
+      </c>
+      <c r="O37" t="n">
+        <v>4</v>
+      </c>
+      <c r="P37" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BOGOTA </t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>URBANISMO EXTERNO LOTE 5 BANCA</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Entregas</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Ronald Forero</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BOGOTA </t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>URBANISMO TRES QUEBRADAS</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Ronald Forero</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Mauricio Andres Cervantes</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>TRES QUEBRADAS</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>JUEVES</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>JUEVES</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+        </is>
+      </c>
+      <c r="O39" t="n">
+        <v>4</v>
+      </c>
+      <c r="P39" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BOGOTA </t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>VERDANIA BOSQUES DE GUAYMARAL</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Ronald Forero</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Leonardo de Jesus Guerrero Cabrera</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>NORTE</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>JUEVES</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>11:00:00</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>VIERNES</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>11:00:00</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
+        </is>
+      </c>
+      <c r="O40" t="n">
+        <v>4</v>
+      </c>
+      <c r="P40" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1</v>
+      </c>
+      <c r="W40" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="X40" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BOGOTA </t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>ZURI - ZENTRAL</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Pedro Mora</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Yenny Paola Munevar Peña</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>ZENTRAL</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>JUEVES</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>VIERNES</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
+        </is>
+      </c>
+      <c r="O41" t="n">
+        <v>4</v>
+      </c>
+      <c r="P41" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1</v>
+      </c>
+      <c r="W41" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="X41" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BOGOTA </t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>MALAGA CASTILLA RESERVADO</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Entregas</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Ronald Forero</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>IBERIA</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr"/>
+      <c r="S42" t="inlineStr"/>
+      <c r="T42" t="inlineStr"/>
+      <c r="U42" t="n">
+        <v>0</v>
+      </c>
+      <c r="V42" t="n">
+        <v>0</v>
+      </c>
+      <c r="W42" t="n">
+        <v>0</v>
+      </c>
+      <c r="X42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BOGOTA </t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>PRUEBA</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>PRUEBA</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>SABADO</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>LUNES</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>2026-03-07, 2026-03-09, 2026-03-14, 2026-03-16, 2026-03-21, 2026-03-24, 2026-03-28</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-24, 2026-03-25</t>
+        </is>
+      </c>
+      <c r="O43" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P43" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr"/>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
+      </c>
+      <c r="V43" t="n">
+        <v>1</v>
+      </c>
+      <c r="W43" t="n">
+        <v>0</v>
+      </c>
+      <c r="X43" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>BARRANQUILLA</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>PUERTA DORADA CRISTALINA</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Germán Baquero</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Kelly Gutierrez</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>PUERTA DORADA</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>JUEVES</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>VIERNES</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
+        </is>
+      </c>
+      <c r="O44" t="n">
+        <v>4</v>
+      </c>
+      <c r="P44" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>2026-03-05, 2026-03-12</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>2026-03-03, 2026-03-06</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>2026-03-05, 2026-03-12</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="U44" t="n">
+        <v>2</v>
+      </c>
+      <c r="V44" t="n">
+        <v>1</v>
+      </c>
+      <c r="W44" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="X44" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>BARRANQUILLA</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>AMARETTO</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>José Luis Suarez</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Abimael Padilla</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>JUEVES</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>VIERNES</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
+        </is>
+      </c>
+      <c r="O45" t="n">
+        <v>4</v>
+      </c>
+      <c r="P45" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>2026-03-05, 2026-03-12</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>2026-03-05, 2026-03-12</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>2026-03-05, 2026-03-12</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr"/>
+      <c r="U45" t="n">
+        <v>2</v>
+      </c>
+      <c r="V45" t="n">
+        <v>0</v>
+      </c>
+      <c r="W45" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="X45" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>BARRANQUILLA</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>RIVERBAY</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>José Luis Suarez</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Orlando Iguaran</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>MARTES</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>MIERCOLES</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>02:00:00</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+        </is>
+      </c>
+      <c r="O46" t="n">
+        <v>4</v>
+      </c>
+      <c r="P46" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>2026-03-03, 2026-03-10</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>2026-03-04, 2026-03-11</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>2026-03-03, 2026-03-10</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>2026-03-04, 2026-03-11</t>
+        </is>
+      </c>
+      <c r="U46" t="n">
+        <v>2</v>
+      </c>
+      <c r="V46" t="n">
+        <v>2</v>
+      </c>
+      <c r="W46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="X46" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>BUCARAMANGA</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>PARQUE ORIENTE SOLEIL</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ejecución/Entregas</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Claudia Cruz</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Luisa Henao</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>PARQUE ORIENTE</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>MARTES</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>MARTES</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25</t>
+        </is>
+      </c>
+      <c r="O47" t="n">
+        <v>4</v>
+      </c>
+      <c r="P47" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>2026-03-03, 2026-03-10</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>2026-03-04, 2026-03-11</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>2026-03-03, 2026-03-10</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>2026-03-04, 2026-03-11</t>
+        </is>
+      </c>
+      <c r="U47" t="n">
+        <v>2</v>
+      </c>
+      <c r="V47" t="n">
+        <v>2</v>
+      </c>
+      <c r="W47" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="X47" t="n">
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>

--- a/output/resumen.xlsx
+++ b/output/resumen.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,122 +429,122 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Sucursal</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Proyecto</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>HC</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Gerente</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Director de obra</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>ValidacionParametrización</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Cluster</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>DiaIntermedia</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>HorarioIntermedia</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>DiaSemanal</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>HorarioSemanal</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>PosibleIntermedia</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>PosibleSemanal</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>ConteoIntermedia</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>ConteoSemanal</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>RealIntermedia</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>RealSemanal</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>CoincidenciasIntermedia</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>CoincidenciasSemanal</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>ConteoCoincidenciasIntermedia</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>ConteoCoincidenciasSemanal</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>CumplimientoIntermedia</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>CumplimientoSemanal</t>
         </is>

--- a/output/resumen.xlsx
+++ b/output/resumen.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,122 +417,122 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Sucursal</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Proyecto</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>HC</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Gerente</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Director de obra</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>ValidacionParametrización</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Cluster</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>DiaIntermedia</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>HorarioIntermedia</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>DiaSemanal</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>HorarioSemanal</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>PosibleIntermedia</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>PosibleSemanal</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>ConteoIntermedia</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>ConteoSemanal</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>RealIntermedia</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>RealSemanal</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>CoincidenciasIntermedia</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>CoincidenciasSemanal</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>ConteoCoincidenciasIntermedia</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>ConteoCoincidenciasSemanal</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>CumplimientoIntermedia</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>CumplimientoSemanal</t>
         </is>

--- a/output/resumen.xlsx
+++ b/output/resumen.xlsx
@@ -3845,289 +3845,117 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>BARRANQUILLA</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>PUERTA DORADA CRISTALINA</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ejecución</t>
-        </is>
-      </c>
+      <c r="A44" t="inlineStr"/>
+      <c r="B44" t="inlineStr"/>
+      <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>Germán Baquero</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Kelly Gutierrez</t>
-        </is>
-      </c>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>PUERTA DORADA</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>JUEVES</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>VIERNES</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
-        </is>
-      </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="O44" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t>2026-03-05, 2026-03-12</t>
-        </is>
-      </c>
-      <c r="R44" t="inlineStr">
-        <is>
-          <t>2026-03-03, 2026-03-06</t>
-        </is>
-      </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>2026-03-05, 2026-03-12</t>
-        </is>
-      </c>
-      <c r="T44" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr"/>
+      <c r="S44" t="inlineStr"/>
+      <c r="T44" t="inlineStr"/>
       <c r="U44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>BARRANQUILLA</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>AMARETTO</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ejecución</t>
-        </is>
-      </c>
+      <c r="A45" t="inlineStr"/>
+      <c r="B45" t="inlineStr"/>
+      <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>José Luis Suarez</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Abimael Padilla</t>
-        </is>
-      </c>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>JUEVES</t>
-        </is>
-      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>VIERNES</t>
-        </is>
-      </c>
+      <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
-        </is>
-      </c>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="O45" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>2026-03-05, 2026-03-12</t>
-        </is>
-      </c>
-      <c r="R45" t="inlineStr">
-        <is>
-          <t>2026-03-05, 2026-03-12</t>
-        </is>
-      </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>2026-03-05, 2026-03-12</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr"/>
+      <c r="S45" t="inlineStr"/>
       <c r="T45" t="inlineStr"/>
       <c r="U45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
         <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>BARRANQUILLA</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>RIVERBAY</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ejecución</t>
-        </is>
-      </c>
+      <c r="A46" t="inlineStr"/>
+      <c r="B46" t="inlineStr"/>
+      <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>José Luis Suarez</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Orlando Iguaran</t>
-        </is>
-      </c>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>MARTES</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>MIERCOLES</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>02:00:00</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
-        </is>
-      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="O46" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q46" t="inlineStr">
-        <is>
-          <t>2026-03-03, 2026-03-10</t>
-        </is>
-      </c>
-      <c r="R46" t="inlineStr">
-        <is>
-          <t>2026-03-04, 2026-03-11</t>
-        </is>
-      </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>2026-03-03, 2026-03-10</t>
-        </is>
-      </c>
-      <c r="T46" t="inlineStr">
-        <is>
-          <t>2026-03-04, 2026-03-11</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr"/>
+      <c r="S46" t="inlineStr"/>
+      <c r="T46" t="inlineStr"/>
       <c r="U46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">

--- a/output/resumen.xlsx
+++ b/output/resumen.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X47"/>
+  <dimension ref="A1:X43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -637,8 +637,16 @@
       <c r="P3" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>2026-03-25, 2026-03-31</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>2026-03-24, 2026-03-25, 2026-03-31</t>
+        </is>
+      </c>
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="n">
@@ -779,35 +787,35 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-09</t>
+          <t>2026-03-02, 2026-03-09, 2026-03-16, 2026-03-24, 2026-03-30</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-11</t>
+          <t>2026-03-04, 2026-03-11, 2026-03-18, 2026-03-25</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-09</t>
+          <t>2026-03-02, 2026-03-09, 2026-03-16, 2026-03-24</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-11</t>
+          <t>2026-03-04, 2026-03-11, 2026-03-18, 2026-03-25</t>
         </is>
       </c>
       <c r="U5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="V5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="W5" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="X5" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -849,12 +857,12 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-03</t>
+          <t>2026-03-02, 2026-03-03, 2026-03-20, 2026-03-21, 2026-03-25, 2026-03-28, 2026-03-30, 2026-03-31</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-03</t>
+          <t>2026-03-02, 2026-03-03, 2026-03-20, 2026-03-21, 2026-03-24, 2026-03-25, 2026-03-28, 2026-03-30, 2026-03-31</t>
         </is>
       </c>
       <c r="S6" t="inlineStr"/>
@@ -997,35 +1005,35 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-09</t>
+          <t>2026-03-02, 2026-03-09, 2026-03-16, 2026-03-25</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-05, 2026-03-11, 2026-03-18, 2026-03-26</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-09</t>
+          <t>2026-03-02, 2026-03-09, 2026-03-16, 2026-03-25</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-05, 2026-03-11, 2026-03-18, 2026-03-26</t>
         </is>
       </c>
       <c r="U8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="V8" t="n">
+        <v>4</v>
+      </c>
+      <c r="W8" t="n">
         <v>1</v>
       </c>
-      <c r="W8" t="n">
-        <v>0.5</v>
-      </c>
       <c r="X8" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -1101,31 +1109,35 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-10</t>
+          <t>2026-03-03, 2026-03-10, 2026-03-12, 2026-03-24</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-04, 2026-03-12, 2026-03-20, 2026-03-26</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-10</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr"/>
+          <t>2026-03-03, 2026-03-10, 2026-03-24</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>2026-03-12, 2026-03-20, 2026-03-26</t>
+        </is>
+      </c>
       <c r="U9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="10">
@@ -1199,35 +1211,35 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-04, 2026-03-05</t>
+          <t>2026-03-02, 2026-03-04, 2026-03-05, 2026-03-12, 2026-03-20, 2026-03-26</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-04, 2026-03-09</t>
+          <t>2026-03-02, 2026-03-04, 2026-03-09, 2026-03-16, 2026-03-24, 2026-03-30</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-05, 2026-03-12, 2026-03-20, 2026-03-26</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-09</t>
+          <t>2026-03-02, 2026-03-09, 2026-03-16, 2026-03-24</t>
         </is>
       </c>
       <c r="U10" t="n">
+        <v>4</v>
+      </c>
+      <c r="V10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W10" t="n">
         <v>1</v>
       </c>
-      <c r="V10" t="n">
-        <v>2</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0.25</v>
-      </c>
       <c r="X10" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1269,12 +1281,12 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-09, 2026-03-16</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-09</t>
+          <t>2026-03-06, 2026-03-09, 2026-03-18</t>
         </is>
       </c>
       <c r="S11" t="inlineStr"/>
@@ -1353,29 +1365,37 @@
       <c r="P12" t="n">
         <v>4</v>
       </c>
-      <c r="Q12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>2026-03-12, 2026-03-19, 2026-03-27</t>
+        </is>
+      </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr"/>
+          <t>2026-03-05, 2026-03-13, 2026-03-27</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>2026-03-12, 2026-03-19, 2026-03-27</t>
+        </is>
+      </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-05, 2026-03-13, 2026-03-27</t>
         </is>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="X12" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="13">
@@ -1441,27 +1461,35 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-03, 2026-03-12, 2026-03-19, 2026-03-26</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
+          <t>2026-03-05, 2026-03-12, 2026-03-20, 2026-03-27</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>2026-03-12, 2026-03-19, 2026-03-26</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>2026-03-20, 2026-03-27</t>
+        </is>
+      </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="14">
@@ -1531,35 +1559,35 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-05</t>
+          <t>2026-03-03, 2026-03-05, 2026-03-12, 2026-03-19</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-06</t>
+          <t>2026-03-03, 2026-03-06, 2026-03-13, 2026-03-26</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-05, 2026-03-12, 2026-03-19</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-06, 2026-03-13</t>
         </is>
       </c>
       <c r="U14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W14" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="X14" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="15">
@@ -1655,12 +1683,12 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-03, 2026-03-04</t>
+          <t>2026-03-02, 2026-03-03, 2026-03-04, 2026-03-12, 2026-03-18, 2026-03-21</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-03, 2026-03-04</t>
+          <t>2026-03-02, 2026-03-03, 2026-03-04, 2026-03-14, 2026-03-18</t>
         </is>
       </c>
       <c r="S16" t="inlineStr"/>
@@ -1751,35 +1779,35 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-09</t>
+          <t>2026-03-04, 2026-03-09, 2026-03-20, 2026-03-26</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-06, 2026-03-13, 2026-03-20, 2026-03-27</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-04, 2026-03-20, 2026-03-26</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-06, 2026-03-13, 2026-03-20, 2026-03-27</t>
         </is>
       </c>
       <c r="U17" t="n">
+        <v>3</v>
+      </c>
+      <c r="V17" t="n">
+        <v>4</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="X17" t="n">
         <v>1</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="X17" t="n">
-        <v>0.25</v>
       </c>
     </row>
     <row r="18">
@@ -1853,35 +1881,35 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-11, 2026-03-18, 2026-03-25</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-04, 2026-03-11, 2026-03-18, 2026-03-25</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-11, 2026-03-18, 2026-03-25</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-04, 2026-03-11, 2026-03-18, 2026-03-25</t>
         </is>
       </c>
       <c r="U18" t="n">
+        <v>3</v>
+      </c>
+      <c r="V18" t="n">
+        <v>4</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="X18" t="n">
         <v>1</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="X18" t="n">
-        <v>0.25</v>
       </c>
     </row>
     <row r="19">
@@ -1947,27 +1975,35 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-03, 2026-03-13, 2026-03-20, 2026-03-27</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr"/>
+          <t>2026-03-05, 2026-03-13, 2026-03-20, 2026-03-27</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>2026-03-13, 2026-03-20, 2026-03-27</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>2026-03-13, 2026-03-20, 2026-03-27</t>
+        </is>
+      </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="20">
@@ -2061,10 +2097,14 @@
       <c r="P21" t="n">
         <v>0</v>
       </c>
-      <c r="Q21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-06, 2026-03-16</t>
         </is>
       </c>
       <c r="S21" t="inlineStr"/>
@@ -2153,31 +2193,35 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-04, 2026-03-11, 2026-03-15, 2026-03-24, 2026-03-30</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-09, 2026-03-15, 2026-03-21, 2026-03-29, 2026-03-30</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr"/>
+          <t>2026-03-04, 2026-03-11</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
       <c r="U22" t="n">
+        <v>2</v>
+      </c>
+      <c r="V22" t="n">
         <v>1</v>
       </c>
-      <c r="V22" t="n">
-        <v>0</v>
-      </c>
       <c r="W22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="X22" t="n">
         <v>0.25</v>
-      </c>
-      <c r="X22" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2359,35 +2403,35 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-10</t>
+          <t>2026-03-03, 2026-03-10, 2026-03-17, 2026-03-24</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-05, 2026-03-12, 2026-03-19, 2026-03-26</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-10</t>
+          <t>2026-03-03, 2026-03-10, 2026-03-17, 2026-03-24</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-05, 2026-03-12, 2026-03-19, 2026-03-26</t>
         </is>
       </c>
       <c r="U25" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="V25" t="n">
+        <v>4</v>
+      </c>
+      <c r="W25" t="n">
         <v>1</v>
       </c>
-      <c r="W25" t="n">
-        <v>0.5</v>
-      </c>
       <c r="X25" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -2453,28 +2497,32 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-04, 2026-03-12, 2026-03-18, 2026-03-31</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-06</t>
-        </is>
-      </c>
-      <c r="S26" t="inlineStr"/>
+          <t>2026-03-04, 2026-03-06, 2026-03-12, 2026-03-18, 2026-03-31</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
       <c r="T26" t="inlineStr">
         <is>
           <t>2026-03-06</t>
         </is>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V26" t="n">
         <v>1</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="X26" t="n">
         <v>0.25</v>
@@ -2519,12 +2567,12 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-10</t>
+          <t>2026-03-03, 2026-03-10, 2026-03-17, 2026-03-20, 2026-03-24</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-10</t>
+          <t>2026-03-03, 2026-03-10, 2026-03-17, 2026-03-20, 2026-03-24</t>
         </is>
       </c>
       <c r="S27" t="inlineStr"/>
@@ -2607,22 +2655,30 @@
       <c r="P28" t="n">
         <v>4</v>
       </c>
-      <c r="Q28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
       <c r="R28" t="inlineStr">
         <is>
           <t>2026-03-05</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr"/>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
       <c r="T28" t="inlineStr"/>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="X28" t="n">
         <v>0</v>
@@ -2753,31 +2809,35 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-09</t>
+          <t>2026-03-02, 2026-03-09, 2026-03-16, 2026-03-24, 2026-03-30</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-09</t>
+          <t>2026-03-02, 2026-03-09, 2026-03-17, 2026-03-25</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-09</t>
-        </is>
-      </c>
-      <c r="T30" t="inlineStr"/>
+          <t>2026-03-02, 2026-03-09, 2026-03-16, 2026-03-24</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>2026-03-17, 2026-03-25</t>
+        </is>
+      </c>
       <c r="U30" t="n">
+        <v>4</v>
+      </c>
+      <c r="V30" t="n">
         <v>2</v>
       </c>
-      <c r="V30" t="n">
-        <v>0</v>
-      </c>
       <c r="W30" t="n">
+        <v>1</v>
+      </c>
+      <c r="X30" t="n">
         <v>0.5</v>
-      </c>
-      <c r="X30" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2905,35 +2965,35 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-03, 2026-03-11, 2026-03-18, 2026-03-25</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-05, 2026-03-12, 2026-03-19</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-03, 2026-03-11, 2026-03-18, 2026-03-25</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-05, 2026-03-12, 2026-03-19</t>
         </is>
       </c>
       <c r="U32" t="n">
+        <v>4</v>
+      </c>
+      <c r="V32" t="n">
+        <v>3</v>
+      </c>
+      <c r="W32" t="n">
         <v>1</v>
       </c>
-      <c r="V32" t="n">
-        <v>1</v>
-      </c>
-      <c r="W32" t="n">
-        <v>0.25</v>
-      </c>
       <c r="X32" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="33">
@@ -3069,35 +3129,35 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-05</t>
+          <t>2026-03-03, 2026-03-05, 2026-03-11, 2026-03-17, 2026-03-24</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05</t>
+          <t>2026-03-04, 2026-03-05, 2026-03-15, 2026-03-19, 2026-03-26</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-03, 2026-03-11, 2026-03-17, 2026-03-24</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-04, 2026-03-19, 2026-03-26</t>
         </is>
       </c>
       <c r="U34" t="n">
+        <v>4</v>
+      </c>
+      <c r="V34" t="n">
+        <v>3</v>
+      </c>
+      <c r="W34" t="n">
         <v>1</v>
       </c>
-      <c r="V34" t="n">
-        <v>1</v>
-      </c>
-      <c r="W34" t="n">
-        <v>0.25</v>
-      </c>
       <c r="X34" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="35">
@@ -3167,27 +3227,35 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr"/>
+          <t>2026-03-04, 2026-03-12, 2026-03-18, 2026-03-26</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>2026-03-12, 2026-03-13, 2026-03-20, 2026-03-28</t>
+        </is>
+      </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr"/>
+          <t>2026-03-04, 2026-03-12, 2026-03-18, 2026-03-26</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>2026-03-13, 2026-03-20, 2026-03-28</t>
+        </is>
+      </c>
       <c r="U35" t="n">
+        <v>4</v>
+      </c>
+      <c r="V35" t="n">
+        <v>3</v>
+      </c>
+      <c r="W35" t="n">
         <v>1</v>
       </c>
-      <c r="V35" t="n">
-        <v>0</v>
-      </c>
-      <c r="W35" t="n">
-        <v>0.25</v>
-      </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="36">
@@ -3229,12 +3297,12 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05</t>
+          <t>2026-03-04, 2026-03-05, 2026-03-17, 2026-03-18, 2026-03-20, 2026-03-27</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05</t>
+          <t>2026-03-04, 2026-03-05, 2026-03-18, 2026-03-20, 2026-03-27</t>
         </is>
       </c>
       <c r="S36" t="inlineStr"/>
@@ -3325,35 +3393,35 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-04, 2026-03-11, 2026-03-18, 2026-03-25</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-05, 2026-03-12, 2026-03-19, 2026-03-26</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-04, 2026-03-11, 2026-03-18, 2026-03-25</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-05, 2026-03-12, 2026-03-19, 2026-03-26</t>
         </is>
       </c>
       <c r="U37" t="n">
+        <v>4</v>
+      </c>
+      <c r="V37" t="n">
+        <v>4</v>
+      </c>
+      <c r="W37" t="n">
         <v>1</v>
       </c>
-      <c r="V37" t="n">
+      <c r="X37" t="n">
         <v>1</v>
-      </c>
-      <c r="W37" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="X37" t="n">
-        <v>0.25</v>
       </c>
     </row>
     <row r="38">
@@ -3481,31 +3549,35 @@
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-04, 2026-03-12, 2026-03-20, 2026-03-27</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="S39" t="inlineStr"/>
+          <t>2026-03-05, 2026-03-12, 2026-03-20, 2026-03-27</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>2026-03-12, 2026-03-20, 2026-03-27</t>
+        </is>
+      </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-05, 2026-03-12, 2026-03-20, 2026-03-27</t>
         </is>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V39" t="n">
+        <v>4</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="X39" t="n">
         <v>1</v>
-      </c>
-      <c r="W39" t="n">
-        <v>0</v>
-      </c>
-      <c r="X39" t="n">
-        <v>0.25</v>
       </c>
     </row>
     <row r="40">
@@ -3579,35 +3651,35 @@
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-05, 2026-03-14, 2026-03-19, 2026-03-28</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-06, 2026-03-18, 2026-03-20, 2026-03-28</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-05, 2026-03-14, 2026-03-19, 2026-03-28</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-06, 2026-03-20, 2026-03-28</t>
         </is>
       </c>
       <c r="U40" t="n">
+        <v>4</v>
+      </c>
+      <c r="V40" t="n">
+        <v>3</v>
+      </c>
+      <c r="W40" t="n">
         <v>1</v>
       </c>
-      <c r="V40" t="n">
-        <v>1</v>
-      </c>
-      <c r="W40" t="n">
-        <v>0.25</v>
-      </c>
       <c r="X40" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="41">
@@ -3673,35 +3745,35 @@
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-05, 2026-03-13, 2026-03-19, 2026-03-27</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-06, 2026-03-13, 2026-03-19, 2026-03-27</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-05, 2026-03-13, 2026-03-19, 2026-03-27</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-06, 2026-03-13, 2026-03-27</t>
         </is>
       </c>
       <c r="U41" t="n">
+        <v>4</v>
+      </c>
+      <c r="V41" t="n">
+        <v>3</v>
+      </c>
+      <c r="W41" t="n">
         <v>1</v>
       </c>
-      <c r="V41" t="n">
-        <v>1</v>
-      </c>
-      <c r="W41" t="n">
-        <v>0.25</v>
-      </c>
       <c r="X41" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="42">
@@ -3815,241 +3887,21 @@
       <c r="P43" t="n">
         <v>4</v>
       </c>
-      <c r="Q43" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="R43" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr"/>
       <c r="S43" t="inlineStr"/>
-      <c r="T43" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
+      <c r="T43" t="inlineStr"/>
       <c r="U43" t="n">
         <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W43" t="n">
         <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr"/>
-      <c r="B44" t="inlineStr"/>
-      <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" t="n">
-        <v>0</v>
-      </c>
-      <c r="P44" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q44" t="inlineStr"/>
-      <c r="R44" t="inlineStr"/>
-      <c r="S44" t="inlineStr"/>
-      <c r="T44" t="inlineStr"/>
-      <c r="U44" t="n">
-        <v>0</v>
-      </c>
-      <c r="V44" t="n">
-        <v>0</v>
-      </c>
-      <c r="W44" t="n">
-        <v>0</v>
-      </c>
-      <c r="X44" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr"/>
-      <c r="B45" t="inlineStr"/>
-      <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="n">
-        <v>0</v>
-      </c>
-      <c r="P45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q45" t="inlineStr"/>
-      <c r="R45" t="inlineStr"/>
-      <c r="S45" t="inlineStr"/>
-      <c r="T45" t="inlineStr"/>
-      <c r="U45" t="n">
-        <v>0</v>
-      </c>
-      <c r="V45" t="n">
-        <v>0</v>
-      </c>
-      <c r="W45" t="n">
-        <v>0</v>
-      </c>
-      <c r="X45" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr"/>
-      <c r="B46" t="inlineStr"/>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
-      <c r="O46" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q46" t="inlineStr"/>
-      <c r="R46" t="inlineStr"/>
-      <c r="S46" t="inlineStr"/>
-      <c r="T46" t="inlineStr"/>
-      <c r="U46" t="n">
-        <v>0</v>
-      </c>
-      <c r="V46" t="n">
-        <v>0</v>
-      </c>
-      <c r="W46" t="n">
-        <v>0</v>
-      </c>
-      <c r="X46" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>BUCARAMANGA</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>PARQUE ORIENTE SOLEIL</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ejecución/Entregas</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Claudia Cruz</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Luisa Henao</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>PARQUE ORIENTE</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>MARTES</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>MARTES</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25</t>
-        </is>
-      </c>
-      <c r="O47" t="n">
-        <v>4</v>
-      </c>
-      <c r="P47" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q47" t="inlineStr">
-        <is>
-          <t>2026-03-03, 2026-03-10</t>
-        </is>
-      </c>
-      <c r="R47" t="inlineStr">
-        <is>
-          <t>2026-03-04, 2026-03-11</t>
-        </is>
-      </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>2026-03-03, 2026-03-10</t>
-        </is>
-      </c>
-      <c r="T47" t="inlineStr">
-        <is>
-          <t>2026-03-04, 2026-03-11</t>
-        </is>
-      </c>
-      <c r="U47" t="n">
-        <v>2</v>
-      </c>
-      <c r="V47" t="n">
-        <v>2</v>
-      </c>
-      <c r="W47" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="X47" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/output/resumen.xlsx
+++ b/output/resumen.xlsx
@@ -639,7 +639,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-03-25, 2026-03-31</t>
+          <t>2026-03-24, 2026-03-25, 2026-03-31</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-11, 2026-03-18, 2026-03-25</t>
+          <t>2026-03-05, 2026-03-12, 2026-03-18, 2026-03-25</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -802,7 +802,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-11, 2026-03-18, 2026-03-25</t>
+          <t>2026-03-05, 2026-03-12, 2026-03-18, 2026-03-25</t>
         </is>
       </c>
       <c r="U5" t="n">
@@ -857,7 +857,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-03, 2026-03-20, 2026-03-21, 2026-03-25, 2026-03-28, 2026-03-30, 2026-03-31</t>
+          <t>2026-03-02, 2026-03-20, 2026-03-24, 2026-03-25, 2026-03-28, 2026-03-30, 2026-03-31</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1005,22 +1005,22 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-09, 2026-03-16, 2026-03-25</t>
+          <t>2026-03-02, 2026-03-09, 2026-03-16, 2026-03-26</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-11, 2026-03-18, 2026-03-26</t>
+          <t>2026-03-05, 2026-03-11, 2026-03-19, 2026-03-26</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-09, 2026-03-16, 2026-03-25</t>
+          <t>2026-03-02, 2026-03-09, 2026-03-16, 2026-03-26</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-11, 2026-03-18, 2026-03-26</t>
+          <t>2026-03-05, 2026-03-11, 2026-03-19, 2026-03-26</t>
         </is>
       </c>
       <c r="U8" t="n">
@@ -1109,22 +1109,22 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-10, 2026-03-12, 2026-03-24</t>
+          <t>2026-03-04, 2026-03-12, 2026-03-20, 2026-03-26</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-12, 2026-03-20, 2026-03-26</t>
+          <t>2026-03-10, 2026-03-12, 2026-03-20, 2026-03-27</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-10, 2026-03-24</t>
+          <t>2026-03-04, 2026-03-12, 2026-03-26</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-03-12, 2026-03-20, 2026-03-26</t>
+          <t>2026-03-12, 2026-03-20, 2026-03-27</t>
         </is>
       </c>
       <c r="U9" t="n">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-04, 2026-03-05, 2026-03-12, 2026-03-20, 2026-03-26</t>
+          <t>2026-03-02, 2026-03-04, 2026-03-07, 2026-03-13, 2026-03-20, 2026-03-26</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-12, 2026-03-20, 2026-03-26</t>
+          <t>2026-03-07, 2026-03-13, 2026-03-20, 2026-03-26</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
@@ -1281,12 +1281,12 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-03-09, 2026-03-16</t>
+          <t>2026-03-09, 2026-03-18</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-09, 2026-03-18</t>
+          <t>2026-03-06, 2026-03-14</t>
         </is>
       </c>
       <c r="S11" t="inlineStr"/>
@@ -1367,35 +1367,35 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-03-12, 2026-03-19, 2026-03-27</t>
+          <t>2026-03-04, 2026-03-13, 2026-03-27</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-13, 2026-03-27</t>
+          <t>2026-03-05, 2026-03-16, 2026-03-27</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>2026-03-12, 2026-03-19, 2026-03-27</t>
+          <t>2026-03-04, 2026-03-13, 2026-03-27</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-13, 2026-03-27</t>
+          <t>2026-03-05, 2026-03-27</t>
         </is>
       </c>
       <c r="U12" t="n">
         <v>3</v>
       </c>
       <c r="V12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W12" t="n">
         <v>0.75</v>
       </c>
       <c r="X12" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="13">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-12, 2026-03-19, 2026-03-26</t>
+          <t>2026-03-03, 2026-03-12, 2026-03-20, 2026-03-27</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>2026-03-12, 2026-03-19, 2026-03-26</t>
+          <t>2026-03-12, 2026-03-20, 2026-03-27</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
@@ -1559,35 +1559,35 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-05, 2026-03-12, 2026-03-19</t>
+          <t>2026-03-03, 2026-03-05, 2026-03-12, 2026-03-24</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-06, 2026-03-13, 2026-03-26</t>
+          <t>2026-03-03, 2026-03-10, 2026-03-14</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-12, 2026-03-19</t>
+          <t>2026-03-05, 2026-03-12</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="U14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W14" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="X14" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="15">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-03, 2026-03-04, 2026-03-12, 2026-03-18, 2026-03-21</t>
+          <t>2026-03-02, 2026-03-03, 2026-03-04, 2026-03-12, 2026-03-18, 2026-03-22</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -1779,35 +1779,35 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-09, 2026-03-20, 2026-03-26</t>
+          <t>2026-03-05, 2026-03-12, 2026-03-20, 2026-03-27</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-13, 2026-03-20, 2026-03-27</t>
+          <t>2026-03-09, 2026-03-13, 2026-03-21, 2026-03-27</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-20, 2026-03-26</t>
+          <t>2026-03-05, 2026-03-12, 2026-03-20, 2026-03-27</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-13, 2026-03-20, 2026-03-27</t>
+          <t>2026-03-13, 2026-03-21, 2026-03-27</t>
         </is>
       </c>
       <c r="U17" t="n">
+        <v>4</v>
+      </c>
+      <c r="V17" t="n">
         <v>3</v>
       </c>
-      <c r="V17" t="n">
-        <v>4</v>
-      </c>
       <c r="W17" t="n">
+        <v>1</v>
+      </c>
+      <c r="X17" t="n">
         <v>0.75</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1881,7 +1881,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-03-11, 2026-03-18, 2026-03-25</t>
+          <t>2026-03-04, 2026-03-11, 2026-03-18, 2026-03-25</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>2026-03-11, 2026-03-18, 2026-03-25</t>
+          <t>2026-03-04, 2026-03-11, 2026-03-18, 2026-03-25</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
@@ -1900,13 +1900,13 @@
         </is>
       </c>
       <c r="U18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V18" t="n">
         <v>4</v>
       </c>
       <c r="W18" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="X18" t="n">
         <v>1</v>
@@ -1975,35 +1975,35 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-13, 2026-03-20, 2026-03-27</t>
+          <t>2026-03-05, 2026-03-13, 2026-03-20, 2026-03-27</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
+          <t>2026-03-06, 2026-03-13, 2026-03-20, 2026-03-27</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
           <t>2026-03-05, 2026-03-13, 2026-03-20, 2026-03-27</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>2026-03-13, 2026-03-20, 2026-03-27</t>
-        </is>
-      </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-03-13, 2026-03-20, 2026-03-27</t>
+          <t>2026-03-06, 2026-03-13, 2026-03-20, 2026-03-27</t>
         </is>
       </c>
       <c r="U19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W19" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="X19" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -2193,17 +2193,17 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-11, 2026-03-15, 2026-03-24, 2026-03-30</t>
+          <t>2026-03-05, 2026-03-15, 2026-03-21, 2026-03-29, 2026-03-30</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-03-09, 2026-03-15, 2026-03-21, 2026-03-29, 2026-03-30</t>
+          <t>2026-03-10, 2026-03-15, 2026-03-21, 2026-03-29, 2026-03-30</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-11</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
@@ -2212,13 +2212,13 @@
         </is>
       </c>
       <c r="U22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V22" t="n">
         <v>1</v>
       </c>
       <c r="W22" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="X22" t="n">
         <v>0.25</v>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-10, 2026-03-17, 2026-03-24</t>
+          <t>2026-03-04, 2026-03-11, 2026-03-18, 2026-03-25</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -2413,7 +2413,7 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-10, 2026-03-17, 2026-03-24</t>
+          <t>2026-03-04, 2026-03-11, 2026-03-18, 2026-03-25</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-06, 2026-03-12, 2026-03-18, 2026-03-31</t>
+          <t>2026-03-04, 2026-03-06, 2026-03-18, 2026-03-27</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -2512,20 +2512,20 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-06, 2026-03-27</t>
         </is>
       </c>
       <c r="U26" t="n">
         <v>1</v>
       </c>
       <c r="V26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W26" t="n">
         <v>0.25</v>
       </c>
       <c r="X26" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="27">
@@ -2655,30 +2655,22 @@
       <c r="P28" t="n">
         <v>4</v>
       </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
+      <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
         <is>
           <t>2026-03-05</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
+      <c r="S28" t="inlineStr"/>
       <c r="T28" t="inlineStr"/>
       <c r="U28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
         <v>0</v>
@@ -2809,35 +2801,35 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-09, 2026-03-16, 2026-03-24, 2026-03-30</t>
+          <t>2026-03-02, 2026-03-09, 2026-03-17, 2026-03-25, 2026-03-30</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
+          <t>2026-03-02, 2026-03-10, 2026-03-17, 2026-03-25</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
           <t>2026-03-02, 2026-03-09, 2026-03-17, 2026-03-25</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>2026-03-02, 2026-03-09, 2026-03-16, 2026-03-24</t>
-        </is>
-      </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>2026-03-17, 2026-03-25</t>
+          <t>2026-03-10, 2026-03-17, 2026-03-25</t>
         </is>
       </c>
       <c r="U30" t="n">
         <v>4</v>
       </c>
       <c r="V30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W30" t="n">
         <v>1</v>
       </c>
       <c r="X30" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="31">
@@ -3129,17 +3121,17 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-05, 2026-03-11, 2026-03-17, 2026-03-24</t>
+          <t>2026-03-04, 2026-03-05, 2026-03-13, 2026-03-18, 2026-03-25</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05, 2026-03-15, 2026-03-19, 2026-03-26</t>
+          <t>2026-03-03, 2026-03-04, 2026-03-09, 2026-03-16, 2026-03-19, 2026-03-26</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-11, 2026-03-17, 2026-03-24</t>
+          <t>2026-03-04, 2026-03-18, 2026-03-25</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
@@ -3148,13 +3140,13 @@
         </is>
       </c>
       <c r="U34" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V34" t="n">
         <v>3</v>
       </c>
       <c r="W34" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="X34" t="n">
         <v>0.75</v>
@@ -3554,7 +3546,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-12, 2026-03-20, 2026-03-27</t>
+          <t>2026-03-02, 2026-03-05, 2026-03-12, 2026-03-20, 2026-03-27</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -3651,35 +3643,35 @@
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-14, 2026-03-19, 2026-03-28</t>
+          <t>2026-03-05, 2026-03-14, 2026-03-20, 2026-03-28</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-18, 2026-03-20, 2026-03-28</t>
+          <t>2026-03-07, 2026-03-18, 2026-03-20, 2026-03-30</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-14, 2026-03-19, 2026-03-28</t>
+          <t>2026-03-05, 2026-03-14, 2026-03-20, 2026-03-28</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-20, 2026-03-28</t>
+          <t>2026-03-07, 2026-03-20</t>
         </is>
       </c>
       <c r="U40" t="n">
         <v>4</v>
       </c>
       <c r="V40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W40" t="n">
         <v>1</v>
       </c>
       <c r="X40" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="41">

--- a/output/resumen.xlsx
+++ b/output/resumen.xlsx
@@ -1015,7 +1015,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-09, 2026-03-16, 2026-03-26</t>
+          <t>2026-03-02, 2026-03-09, 2026-03-16</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -1024,13 +1024,13 @@
         </is>
       </c>
       <c r="U8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V8" t="n">
         <v>4</v>
       </c>
       <c r="W8" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="X8" t="n">
         <v>1</v>
@@ -1119,7 +1119,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-12, 2026-03-26</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
@@ -1128,13 +1128,13 @@
         </is>
       </c>
       <c r="U9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V9" t="n">
         <v>3</v>
       </c>
       <c r="W9" t="n">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
       <c r="X9" t="n">
         <v>0.75</v>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>2026-03-07, 2026-03-13, 2026-03-20, 2026-03-26</t>
+          <t>2026-03-13, 2026-03-20, 2026-03-26</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
@@ -1230,13 +1230,13 @@
         </is>
       </c>
       <c r="U10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V10" t="n">
         <v>4</v>
       </c>
       <c r="W10" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="X10" t="n">
         <v>1</v>
@@ -1377,7 +1377,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-13, 2026-03-27</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
@@ -1386,13 +1386,13 @@
         </is>
       </c>
       <c r="U12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V12" t="n">
         <v>2</v>
       </c>
       <c r="W12" t="n">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
       <c r="X12" t="n">
         <v>0.5</v>
@@ -1789,7 +1789,7 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-12, 2026-03-20, 2026-03-27</t>
+          <t>2026-03-05, 2026-03-12</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
@@ -1798,13 +1798,13 @@
         </is>
       </c>
       <c r="U17" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="V17" t="n">
         <v>3</v>
       </c>
       <c r="W17" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="X17" t="n">
         <v>0.75</v>
@@ -2206,22 +2206,18 @@
           <t>2026-03-05</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>2026-03-21</t>
-        </is>
-      </c>
+      <c r="T22" t="inlineStr"/>
       <c r="U22" t="n">
         <v>1</v>
       </c>
       <c r="V22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
         <v>0.25</v>
       </c>
       <c r="X22" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -3653,7 +3649,7 @@
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-14, 2026-03-20, 2026-03-28</t>
+          <t>2026-03-05, 2026-03-20</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
@@ -3662,13 +3658,13 @@
         </is>
       </c>
       <c r="U40" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="V40" t="n">
         <v>2</v>
       </c>
       <c r="W40" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="X40" t="n">
         <v>0.5</v>
